--- a/Applied-Research Project/06-LLM-Investigation/05_Comparison/LLM_Scoring_Comparison.xlsx
+++ b/Applied-Research Project/06-LLM-Investigation/05_Comparison/LLM_Scoring_Comparison.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darra\Documents\GitHub\applied-research-project\Applied-Research Project\06-LLM-Investigation\05_Comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{C6B912ED-FEFC-4370-9EB8-384D10891953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -297,21 +297,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -324,6 +309,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,18 +670,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="F1" s="14" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="F1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G2" s="10">
@@ -705,16 +705,16 @@
       <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="24" t="s">
         <v>19</v>
       </c>
     </row>
@@ -725,10 +725,10 @@
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -737,16 +737,16 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -757,10 +757,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -769,16 +769,16 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="24" t="s">
         <v>24</v>
       </c>
     </row>
@@ -789,10 +789,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -843,27 +843,27 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="17"/>
-    <col min="4" max="4" width="15.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="17"/>
-    <col min="6" max="6" width="14.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="35.21875" style="17" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="17"/>
+    <col min="1" max="3" width="8.88671875" style="12"/>
+    <col min="4" max="4" width="15.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="12"/>
+    <col min="6" max="6" width="14.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="35.21875" style="12" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="F1" s="14" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="F1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G2" s="11">
@@ -877,129 +877,135 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="F5" s="13" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="F5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="F7" s="13" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="F7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="24" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
+      <c r="A10" s="20"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
@@ -1008,12 +1014,6 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1024,27 +1024,27 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="17"/>
-    <col min="4" max="4" width="15.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="17"/>
-    <col min="6" max="6" width="14.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="35.21875" style="17" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="17"/>
+    <col min="1" max="3" width="8.88671875" style="12"/>
+    <col min="4" max="4" width="15.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="12"/>
+    <col min="6" max="6" width="14.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="35.21875" style="12" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="F1" s="14" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="F1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G2" s="11">
@@ -1058,129 +1058,135 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="F5" s="13" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="F5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="F7" s="13" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="F7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="24" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
+      <c r="A10" s="20"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
@@ -1189,12 +1195,6 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
